--- a/exports/GODREJPROP_full_report.xlsx
+++ b/exports/GODREJPROP_full_report.xlsx
@@ -18,9 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -51,10 +53,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -420,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q73"/>
+  <dimension ref="A1:U73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -509,6 +512,26 @@
           <t>candles_held</t>
         </is>
       </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>expiry</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>reached_expiry</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>rule_trades</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>rule_wins</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -534,22 +557,22 @@
         <v>5.02</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>44579.55208333334</v>
+        <v>44580.38541666666</v>
       </c>
       <c r="H2" t="n">
-        <v>1903.6</v>
+        <v>1828.4</v>
       </c>
       <c r="I2" t="n">
         <v>1872.075370598138</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>8.166666666666666</v>
+        <v>9</v>
       </c>
       <c r="K2" t="n">
-        <v>-0.68</v>
+        <v>-4.61</v>
       </c>
       <c r="L2" t="n">
-        <v>1.13</v>
+        <v>5.02</v>
       </c>
       <c r="M2" t="n">
         <v>0.36</v>
@@ -564,7 +587,19 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S2" t="b">
+        <v>0</v>
+      </c>
+      <c r="T2" t="n">
+        <v>1</v>
+      </c>
+      <c r="U2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -591,19 +626,19 @@
         <v>9.27</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>44593.55208333334</v>
+        <v>44594.38541666666</v>
       </c>
       <c r="H3" t="n">
-        <v>1729.95</v>
+        <v>1769.65</v>
       </c>
       <c r="I3" t="n">
         <v>1764.8254791667</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>13.16666666666667</v>
+        <v>14</v>
       </c>
       <c r="K3" t="n">
-        <v>5.38</v>
+        <v>3.21</v>
       </c>
       <c r="L3" t="n">
         <v>3.81</v>
@@ -621,7 +656,19 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S3" t="b">
+        <v>1</v>
+      </c>
+      <c r="T3" t="n">
+        <v>2</v>
+      </c>
+      <c r="U3" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -648,28 +695,28 @@
         <v>10.79</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>44595.55208333334</v>
+        <v>44596.38541666666</v>
       </c>
       <c r="H4" t="n">
-        <v>1663.95</v>
+        <v>1522.95</v>
       </c>
       <c r="I4" t="n">
         <v>1612.349551520927</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>1.166666666666667</v>
+        <v>2</v>
       </c>
       <c r="K4" t="n">
-        <v>-5.97</v>
+        <v>-13.94</v>
       </c>
       <c r="L4" t="n">
-        <v>6.67</v>
+        <v>15.18</v>
       </c>
       <c r="M4" t="n">
-        <v>-0</v>
+        <v>9.789999999999999</v>
       </c>
       <c r="N4" t="n">
-        <v>6.36</v>
+        <v>9.31</v>
       </c>
       <c r="O4" t="n">
         <v>2.72</v>
@@ -678,7 +725,19 @@
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>44616</v>
+      </c>
+      <c r="S4" t="b">
+        <v>0</v>
+      </c>
+      <c r="T4" t="n">
+        <v>1</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -705,19 +764,19 @@
         <v>15.11</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>44636.38541666666</v>
+        <v>44636.55208333334</v>
       </c>
       <c r="H5" t="n">
-        <v>1511.75</v>
+        <v>1526</v>
       </c>
       <c r="I5" t="n">
         <v>1515.875196198684</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>40</v>
+        <v>40.16666666666666</v>
       </c>
       <c r="K5" t="n">
-        <v>0.74</v>
+        <v>-0.2</v>
       </c>
       <c r="L5" t="n">
         <v>6.77</v>
@@ -735,7 +794,19 @@
         <v>1</v>
       </c>
       <c r="Q5" t="n">
-        <v>55</v>
+        <v>56</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>44616</v>
+      </c>
+      <c r="S5" t="b">
+        <v>1</v>
+      </c>
+      <c r="T5" t="n">
+        <v>2</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -762,19 +833,19 @@
         <v>8.640000000000001</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>44664.38541666666</v>
+        <v>44664.55208333334</v>
       </c>
       <c r="H6" t="n">
-        <v>1614.1</v>
+        <v>1600</v>
       </c>
       <c r="I6" t="n">
         <v>1608.544736412921</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>27.83333333333333</v>
+        <v>28</v>
       </c>
       <c r="K6" t="n">
-        <v>5.77</v>
+        <v>4.85</v>
       </c>
       <c r="L6" t="n">
         <v>1.17</v>
@@ -792,7 +863,19 @@
         <v>1</v>
       </c>
       <c r="Q6" t="n">
-        <v>38</v>
+        <v>39</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>44651</v>
+      </c>
+      <c r="S6" t="b">
+        <v>1</v>
+      </c>
+      <c r="T6" t="n">
+        <v>2</v>
+      </c>
+      <c r="U6" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -819,19 +902,19 @@
         <v>6.03</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>44680.55208333334</v>
+        <v>44683.38541666666</v>
       </c>
       <c r="H7" t="n">
-        <v>1570</v>
+        <v>1620.4</v>
       </c>
       <c r="I7" t="n">
         <v>1615.140276976203</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>16</v>
+        <v>18.83333333333333</v>
       </c>
       <c r="K7" t="n">
-        <v>1.88</v>
+        <v>-1.28</v>
       </c>
       <c r="L7" t="n">
         <v>1.76</v>
@@ -849,7 +932,19 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>44679</v>
+      </c>
+      <c r="S7" t="b">
+        <v>1</v>
+      </c>
+      <c r="T7" t="n">
+        <v>2</v>
+      </c>
+      <c r="U7" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -876,28 +971,28 @@
         <v>9.539999999999999</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>44685.55208333334</v>
+        <v>44686.38541666666</v>
       </c>
       <c r="H8" t="n">
-        <v>1553.45</v>
+        <v>1473.3</v>
       </c>
       <c r="I8" t="n">
         <v>1507.083024010393</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>2.166666666666667</v>
+        <v>3</v>
       </c>
       <c r="K8" t="n">
-        <v>-4.13</v>
+        <v>-9.08</v>
       </c>
       <c r="L8" t="n">
-        <v>5.21</v>
+        <v>9.24</v>
       </c>
       <c r="M8" t="n">
         <v>0.93</v>
       </c>
       <c r="N8" t="n">
-        <v>4.1</v>
+        <v>6.02</v>
       </c>
       <c r="O8" t="n">
         <v>3.18</v>
@@ -906,7 +1001,19 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>44707</v>
+      </c>
+      <c r="S8" t="b">
+        <v>0</v>
+      </c>
+      <c r="T8" t="n">
+        <v>1</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -933,19 +1040,19 @@
         <v>13.4</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>44711.55208333334</v>
+        <v>44712.38541666666</v>
       </c>
       <c r="H9" t="n">
-        <v>1357</v>
+        <v>1380.85</v>
       </c>
       <c r="I9" t="n">
         <v>1366.18985449906</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>25.16666666666667</v>
+        <v>26</v>
       </c>
       <c r="K9" t="n">
-        <v>7.89</v>
+        <v>6.28</v>
       </c>
       <c r="L9" t="n">
         <v>6.19</v>
@@ -963,7 +1070,19 @@
         <v>1</v>
       </c>
       <c r="Q9" t="n">
-        <v>36</v>
+        <v>37</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>44707</v>
+      </c>
+      <c r="S9" t="b">
+        <v>1</v>
+      </c>
+      <c r="T9" t="n">
+        <v>2</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="10">
@@ -990,28 +1109,28 @@
         <v>8.140000000000001</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>44722.55208333334</v>
+        <v>44725.38541666666</v>
       </c>
       <c r="H10" t="n">
-        <v>1310.7</v>
+        <v>1257</v>
       </c>
       <c r="I10" t="n">
         <v>1297.863439766199</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>10.16666666666667</v>
+        <v>13</v>
       </c>
       <c r="K10" t="n">
-        <v>-5.08</v>
+        <v>-8.970000000000001</v>
       </c>
       <c r="L10" t="n">
-        <v>5.99</v>
+        <v>10.82</v>
       </c>
       <c r="M10" t="n">
-        <v>1.92</v>
+        <v>3.4</v>
       </c>
       <c r="N10" t="n">
-        <v>4.54</v>
+        <v>4.78</v>
       </c>
       <c r="O10" t="n">
         <v>3.02</v>
@@ -1020,7 +1139,19 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>44742</v>
+      </c>
+      <c r="S10" t="b">
+        <v>0</v>
+      </c>
+      <c r="T10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -1047,19 +1178,19 @@
         <v>8.76</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>44747.55208333334</v>
+        <v>44748.38541666666</v>
       </c>
       <c r="H11" t="n">
-        <v>1233.55</v>
+        <v>1267.5</v>
       </c>
       <c r="I11" t="n">
         <v>1264.899749432114</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>22.16666666666667</v>
+        <v>23</v>
       </c>
       <c r="K11" t="n">
-        <v>1.87</v>
+        <v>-0.84</v>
       </c>
       <c r="L11" t="n">
         <v>1.64</v>
@@ -1077,7 +1208,19 @@
         <v>1</v>
       </c>
       <c r="Q11" t="n">
-        <v>34</v>
+        <v>35</v>
+      </c>
+      <c r="R11" s="3" t="n">
+        <v>44742</v>
+      </c>
+      <c r="S11" t="b">
+        <v>1</v>
+      </c>
+      <c r="T11" t="n">
+        <v>2</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="12">
@@ -1104,19 +1247,19 @@
         <v>8.83</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>44775.55208333334</v>
+        <v>44776.38541666666</v>
       </c>
       <c r="H12" t="n">
-        <v>1459.9</v>
+        <v>1416.85</v>
       </c>
       <c r="I12" t="n">
         <v>1432.155488532199</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>27.16666666666667</v>
+        <v>28</v>
       </c>
       <c r="K12" t="n">
-        <v>15.18</v>
+        <v>11.78</v>
       </c>
       <c r="L12" t="n">
         <v>3.46</v>
@@ -1134,7 +1277,19 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>40</v>
+        <v>41</v>
+      </c>
+      <c r="R12" s="3" t="n">
+        <v>44770</v>
+      </c>
+      <c r="S12" t="b">
+        <v>1</v>
+      </c>
+      <c r="T12" t="n">
+        <v>2</v>
+      </c>
+      <c r="U12" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="13">
@@ -1161,19 +1316,19 @@
         <v>10.06</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>44797.55208333334</v>
+        <v>44798.38541666666</v>
       </c>
       <c r="H13" t="n">
-        <v>1342.35</v>
+        <v>1388.75</v>
       </c>
       <c r="I13" t="n">
         <v>1385.574061959541</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>21.16666666666667</v>
+        <v>22</v>
       </c>
       <c r="K13" t="n">
-        <v>5.26</v>
+        <v>1.98</v>
       </c>
       <c r="L13" t="n">
         <v>4.17</v>
@@ -1182,7 +1337,7 @@
         <v>1.1</v>
       </c>
       <c r="N13" t="n">
-        <v>1.88</v>
+        <v>2.67</v>
       </c>
       <c r="O13" t="n">
         <v>-2.8</v>
@@ -1191,7 +1346,19 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="R13" s="3" t="n">
+        <v>44798</v>
+      </c>
+      <c r="S13" t="b">
+        <v>0</v>
+      </c>
+      <c r="T13" t="n">
+        <v>1</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="14">
@@ -1218,19 +1385,19 @@
         <v>7.62</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>44819.55208333334</v>
+        <v>44820.38541666666</v>
       </c>
       <c r="H14" t="n">
-        <v>1386</v>
+        <v>1346.1</v>
       </c>
       <c r="I14" t="n">
         <v>1373.0034507435</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>21.16666666666667</v>
+        <v>22</v>
       </c>
       <c r="K14" t="n">
-        <v>-0.2</v>
+        <v>-3.07</v>
       </c>
       <c r="L14" t="n">
         <v>3.76</v>
@@ -1239,7 +1406,7 @@
         <v>3.36</v>
       </c>
       <c r="N14" t="n">
-        <v>2.45</v>
+        <v>3.92</v>
       </c>
       <c r="O14" t="n">
         <v>2.67</v>
@@ -1248,7 +1415,19 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="R14" s="3" t="n">
+        <v>44833</v>
+      </c>
+      <c r="S14" t="b">
+        <v>0</v>
+      </c>
+      <c r="T14" t="n">
+        <v>1</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -1275,19 +1454,19 @@
         <v>9.35</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>44865.38541666666</v>
+        <v>44865.55208333334</v>
       </c>
       <c r="H15" t="n">
-        <v>1243.3</v>
+        <v>1267</v>
       </c>
       <c r="I15" t="n">
         <v>1245.546336252213</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>45</v>
+        <v>45.16666666666666</v>
       </c>
       <c r="K15" t="n">
-        <v>7.64</v>
+        <v>5.88</v>
       </c>
       <c r="L15" t="n">
         <v>4.38</v>
@@ -1305,7 +1484,19 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>58</v>
+        <v>59</v>
+      </c>
+      <c r="R15" s="3" t="n">
+        <v>44833</v>
+      </c>
+      <c r="S15" t="b">
+        <v>1</v>
+      </c>
+      <c r="T15" t="n">
+        <v>3</v>
+      </c>
+      <c r="U15" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="16">
@@ -1332,22 +1523,22 @@
         <v>6</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>44874.38541666666</v>
+        <v>44874.55208333334</v>
       </c>
       <c r="H16" t="n">
-        <v>1214.05</v>
+        <v>1167.6</v>
       </c>
       <c r="I16" t="n">
         <v>1202.362604994711</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>8.833333333333334</v>
+        <v>9</v>
       </c>
       <c r="K16" t="n">
-        <v>-4.18</v>
+        <v>-7.85</v>
       </c>
       <c r="L16" t="n">
-        <v>6.38</v>
+        <v>8.07</v>
       </c>
       <c r="M16" t="n">
         <v>0.48</v>
@@ -1362,7 +1553,19 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R16" s="3" t="n">
+        <v>44889</v>
+      </c>
+      <c r="S16" t="b">
+        <v>0</v>
+      </c>
+      <c r="T16" t="n">
+        <v>1</v>
+      </c>
+      <c r="U16" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -1389,25 +1592,25 @@
         <v>9.52</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>44875.55208333334</v>
+        <v>44876.38541666666</v>
       </c>
       <c r="H17" t="n">
-        <v>1239</v>
+        <v>1296.5</v>
       </c>
       <c r="I17" t="n">
         <v>1278.744028239654</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>1</v>
+        <v>1.833333333333333</v>
       </c>
       <c r="K17" t="n">
-        <v>-6.12</v>
+        <v>-11.04</v>
       </c>
       <c r="L17" t="n">
-        <v>6.63</v>
+        <v>11.6</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>0.65</v>
       </c>
       <c r="N17" t="n">
         <v>6.12</v>
@@ -1419,7 +1622,19 @@
         <v>1</v>
       </c>
       <c r="Q17" t="n">
-        <v>3</v>
+        <v>4</v>
+      </c>
+      <c r="R17" s="3" t="n">
+        <v>44889</v>
+      </c>
+      <c r="S17" t="b">
+        <v>0</v>
+      </c>
+      <c r="T17" t="n">
+        <v>1</v>
+      </c>
+      <c r="U17" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -1446,19 +1661,19 @@
         <v>10.09</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>44903.55208333334</v>
+        <v>44904.38541666666</v>
       </c>
       <c r="H18" t="n">
-        <v>1301.5</v>
+        <v>1285.55</v>
       </c>
       <c r="I18" t="n">
         <v>1294.100297113471</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>27.16666666666667</v>
+        <v>28</v>
       </c>
       <c r="K18" t="n">
-        <v>0.39</v>
+        <v>-0.84</v>
       </c>
       <c r="L18" t="n">
         <v>4.2</v>
@@ -1476,7 +1691,19 @@
         <v>1</v>
       </c>
       <c r="Q18" t="n">
-        <v>40</v>
+        <v>41</v>
+      </c>
+      <c r="R18" s="3" t="n">
+        <v>44889</v>
+      </c>
+      <c r="S18" t="b">
+        <v>1</v>
+      </c>
+      <c r="T18" t="n">
+        <v>2</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="19">
@@ -1503,19 +1730,19 @@
         <v>5.77</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>44987.55208333334</v>
+        <v>44988.38541666666</v>
       </c>
       <c r="H19" t="n">
-        <v>1125</v>
+        <v>1171.95</v>
       </c>
       <c r="I19" t="n">
         <v>1130.500776370613</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>83.16666666666667</v>
+        <v>84</v>
       </c>
       <c r="K19" t="n">
-        <v>12.49</v>
+        <v>8.84</v>
       </c>
       <c r="L19" t="n">
         <v>4.52</v>
@@ -1524,7 +1751,7 @@
         <v>1.91</v>
       </c>
       <c r="N19" t="n">
-        <v>3.16</v>
+        <v>3.72</v>
       </c>
       <c r="O19" t="n">
         <v>-1.96</v>
@@ -1533,7 +1760,19 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>116</v>
+        <v>117</v>
+      </c>
+      <c r="R19" s="3" t="n">
+        <v>44924</v>
+      </c>
+      <c r="S19" t="b">
+        <v>1</v>
+      </c>
+      <c r="T19" t="n">
+        <v>4</v>
+      </c>
+      <c r="U19" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="20">
@@ -1560,22 +1799,22 @@
         <v>7.03</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>44998.38541666666</v>
+        <v>44998.55208333334</v>
       </c>
       <c r="H20" t="n">
-        <v>1140</v>
+        <v>1121.5</v>
       </c>
       <c r="I20" t="n">
         <v>1123.188969744948</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>10</v>
+        <v>10.16666666666667</v>
       </c>
       <c r="K20" t="n">
-        <v>-2.73</v>
+        <v>-4.3</v>
       </c>
       <c r="L20" t="n">
-        <v>3.58</v>
+        <v>4.42</v>
       </c>
       <c r="M20" t="n">
         <v>1.28</v>
@@ -1590,7 +1829,19 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R20" s="3" t="n">
+        <v>45014</v>
+      </c>
+      <c r="S20" t="b">
+        <v>0</v>
+      </c>
+      <c r="T20" t="n">
+        <v>1</v>
+      </c>
+      <c r="U20" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1617,19 +1868,19 @@
         <v>6.22</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>45021.55208333334</v>
+        <v>45022.38541666666</v>
       </c>
       <c r="H21" t="n">
-        <v>1055</v>
+        <v>1123</v>
       </c>
       <c r="I21" t="n">
         <v>1070.304825387283</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>23</v>
+        <v>23.83333333333333</v>
       </c>
       <c r="K21" t="n">
-        <v>5.93</v>
+        <v>-0.13</v>
       </c>
       <c r="L21" t="n">
         <v>1.92</v>
@@ -1638,7 +1889,7 @@
         <v>1.55</v>
       </c>
       <c r="N21" t="n">
-        <v>1.88</v>
+        <v>6.64</v>
       </c>
       <c r="O21" t="n">
         <v>-3.41</v>
@@ -1647,7 +1898,19 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>31</v>
+        <v>32</v>
+      </c>
+      <c r="R21" s="3" t="n">
+        <v>45014</v>
+      </c>
+      <c r="S21" t="b">
+        <v>1</v>
+      </c>
+      <c r="T21" t="n">
+        <v>2</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="22">
@@ -1674,19 +1937,19 @@
         <v>9.26</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>45063.55208333334</v>
+        <v>45064.38541666666</v>
       </c>
       <c r="H22" t="n">
-        <v>1385</v>
+        <v>1309.35</v>
       </c>
       <c r="I22" t="n">
         <v>1319.905537866649</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>41.16666666666666</v>
+        <v>42</v>
       </c>
       <c r="K22" t="n">
-        <v>23.33</v>
+        <v>16.59</v>
       </c>
       <c r="L22" t="n">
         <v>6.18</v>
@@ -1695,7 +1958,7 @@
         <v>0.48</v>
       </c>
       <c r="N22" t="n">
-        <v>1.33</v>
+        <v>5.7</v>
       </c>
       <c r="O22" t="n">
         <v>6.64</v>
@@ -1704,7 +1967,19 @@
         <v>1</v>
       </c>
       <c r="Q22" t="n">
-        <v>54</v>
+        <v>55</v>
+      </c>
+      <c r="R22" s="3" t="n">
+        <v>45043</v>
+      </c>
+      <c r="S22" t="b">
+        <v>1</v>
+      </c>
+      <c r="T22" t="n">
+        <v>2</v>
+      </c>
+      <c r="U22" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="23">
@@ -1731,22 +2006,22 @@
         <v>10.98</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>45077.55208333334</v>
+        <v>45078.38541666666</v>
       </c>
       <c r="H23" t="n">
-        <v>1395</v>
+        <v>1412.7</v>
       </c>
       <c r="I23" t="n">
         <v>1403.44252302561</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>13.16666666666667</v>
+        <v>14</v>
       </c>
       <c r="K23" t="n">
-        <v>-6.54</v>
+        <v>-7.89</v>
       </c>
       <c r="L23" t="n">
-        <v>6.74</v>
+        <v>8.550000000000001</v>
       </c>
       <c r="M23" t="n">
         <v>0.84</v>
@@ -1761,7 +2036,19 @@
         <v>1</v>
       </c>
       <c r="Q23" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R23" s="3" t="n">
+        <v>45071</v>
+      </c>
+      <c r="S23" t="b">
+        <v>1</v>
+      </c>
+      <c r="T23" t="n">
+        <v>2</v>
+      </c>
+      <c r="U23" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="24">
@@ -1788,19 +2075,19 @@
         <v>5.16</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>45139.55208333334</v>
+        <v>45140.38541666666</v>
       </c>
       <c r="H24" t="n">
-        <v>1694</v>
+        <v>1655</v>
       </c>
       <c r="I24" t="n">
         <v>1666.230477134649</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>61.16666666666666</v>
+        <v>62</v>
       </c>
       <c r="K24" t="n">
-        <v>19.91</v>
+        <v>17.15</v>
       </c>
       <c r="L24" t="n">
         <v>1.36</v>
@@ -1818,7 +2105,19 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>86</v>
+        <v>87</v>
+      </c>
+      <c r="R24" s="3" t="n">
+        <v>45105</v>
+      </c>
+      <c r="S24" t="b">
+        <v>1</v>
+      </c>
+      <c r="T24" t="n">
+        <v>3</v>
+      </c>
+      <c r="U24" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="25">
@@ -1845,19 +2144,19 @@
         <v>7.45</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>45161.55208333334</v>
+        <v>45162.38541666666</v>
       </c>
       <c r="H25" t="n">
-        <v>1597.6</v>
+        <v>1624.95</v>
       </c>
       <c r="I25" t="n">
         <v>1603.951891864429</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>21.16666666666667</v>
+        <v>22</v>
       </c>
       <c r="K25" t="n">
-        <v>3.47</v>
+        <v>1.82</v>
       </c>
       <c r="L25" t="n">
         <v>3.59</v>
@@ -1875,7 +2174,19 @@
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="R25" s="3" t="n">
+        <v>45169</v>
+      </c>
+      <c r="S25" t="b">
+        <v>0</v>
+      </c>
+      <c r="T25" t="n">
+        <v>1</v>
+      </c>
+      <c r="U25" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="26">
@@ -1902,19 +2213,19 @@
         <v>4.92</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>45187.55208333334</v>
+        <v>45189.38541666666</v>
       </c>
       <c r="H26" t="n">
-        <v>1619.75</v>
+        <v>1607.15</v>
       </c>
       <c r="I26" t="n">
         <v>1619.554080971079</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>25.16666666666667</v>
+        <v>27</v>
       </c>
       <c r="K26" t="n">
-        <v>-0.32</v>
+        <v>-1.1</v>
       </c>
       <c r="L26" t="n">
         <v>2.4</v>
@@ -1932,7 +2243,19 @@
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>36</v>
+        <v>37</v>
+      </c>
+      <c r="R26" s="3" t="n">
+        <v>45169</v>
+      </c>
+      <c r="S26" t="b">
+        <v>1</v>
+      </c>
+      <c r="T26" t="n">
+        <v>2</v>
+      </c>
+      <c r="U26" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="27">
@@ -1959,28 +2282,28 @@
         <v>6.17</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>45204.55208333334</v>
+        <v>45205.38541666666</v>
       </c>
       <c r="H27" t="n">
-        <v>1595.35</v>
+        <v>1634.7</v>
       </c>
       <c r="I27" t="n">
         <v>1625.656538790932</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>15.16666666666667</v>
+        <v>16</v>
       </c>
       <c r="K27" t="n">
-        <v>0.73</v>
+        <v>-1.71</v>
       </c>
       <c r="L27" t="n">
-        <v>1.73</v>
+        <v>1.89</v>
       </c>
       <c r="M27" t="n">
         <v>0.89</v>
       </c>
       <c r="N27" t="n">
-        <v>3.19</v>
+        <v>4.84</v>
       </c>
       <c r="O27" t="n">
         <v>-1.81</v>
@@ -1989,7 +2312,19 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R27" s="3" t="n">
+        <v>45197</v>
+      </c>
+      <c r="S27" t="b">
+        <v>1</v>
+      </c>
+      <c r="T27" t="n">
+        <v>2</v>
+      </c>
+      <c r="U27" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="28">
@@ -2016,19 +2351,19 @@
         <v>6.37</v>
       </c>
       <c r="G28" s="1" t="n">
-        <v>45219.55208333334</v>
+        <v>45222.38541666666</v>
       </c>
       <c r="H28" t="n">
-        <v>1649</v>
+        <v>1620.75</v>
       </c>
       <c r="I28" t="n">
         <v>1626.406996249843</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>14.16666666666667</v>
+        <v>17</v>
       </c>
       <c r="K28" t="n">
-        <v>0.87</v>
+        <v>-0.85</v>
       </c>
       <c r="L28" t="n">
         <v>2.18</v>
@@ -2046,7 +2381,19 @@
         <v>1</v>
       </c>
       <c r="Q28" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R28" s="3" t="n">
+        <v>45225</v>
+      </c>
+      <c r="S28" t="b">
+        <v>0</v>
+      </c>
+      <c r="T28" t="n">
+        <v>1</v>
+      </c>
+      <c r="U28" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="29">
@@ -2073,22 +2420,22 @@
         <v>6.35</v>
       </c>
       <c r="G29" s="1" t="n">
-        <v>45230.55208333334</v>
+        <v>45231.38541666666</v>
       </c>
       <c r="H29" t="n">
-        <v>1660.9</v>
+        <v>1677.75</v>
       </c>
       <c r="I29" t="n">
         <v>1665.236374531369</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>8.166666666666666</v>
+        <v>9</v>
       </c>
       <c r="K29" t="n">
-        <v>-2.48</v>
+        <v>-3.52</v>
       </c>
       <c r="L29" t="n">
-        <v>2.92</v>
+        <v>4.77</v>
       </c>
       <c r="M29" t="n">
         <v>0.63</v>
@@ -2103,7 +2450,19 @@
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R29" s="3" t="n">
+        <v>45225</v>
+      </c>
+      <c r="S29" t="b">
+        <v>1</v>
+      </c>
+      <c r="T29" t="n">
+        <v>2</v>
+      </c>
+      <c r="U29" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="30">
@@ -2130,19 +2489,19 @@
         <v>5.08</v>
       </c>
       <c r="G30" s="1" t="n">
-        <v>45280.38541666666</v>
+        <v>45280.55208333334</v>
       </c>
       <c r="H30" t="n">
-        <v>1954.65</v>
+        <v>1883.35</v>
       </c>
       <c r="I30" t="n">
         <v>1940.914291578193</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>49</v>
+        <v>49.16666666666666</v>
       </c>
       <c r="K30" t="n">
-        <v>16.5</v>
+        <v>12.25</v>
       </c>
       <c r="L30" t="n">
         <v>1.06</v>
@@ -2160,7 +2519,19 @@
         <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>68</v>
+        <v>69</v>
+      </c>
+      <c r="R30" s="3" t="n">
+        <v>45260</v>
+      </c>
+      <c r="S30" t="b">
+        <v>1</v>
+      </c>
+      <c r="T30" t="n">
+        <v>2</v>
+      </c>
+      <c r="U30" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="31">
@@ -2187,22 +2558,22 @@
         <v>8.6</v>
       </c>
       <c r="G31" s="1" t="n">
-        <v>45293.55208333334</v>
+        <v>45294.38541666666</v>
       </c>
       <c r="H31" t="n">
-        <v>2017.75</v>
+        <v>2053</v>
       </c>
       <c r="I31" t="n">
         <v>2043.907169749954</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>13</v>
+        <v>13.83333333333333</v>
       </c>
       <c r="K31" t="n">
-        <v>-7.14</v>
+        <v>-9.01</v>
       </c>
       <c r="L31" t="n">
-        <v>8</v>
+        <v>9.31</v>
       </c>
       <c r="M31" t="n">
         <v>1.27</v>
@@ -2217,7 +2588,19 @@
         <v>1</v>
       </c>
       <c r="Q31" t="n">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="R31" s="3" t="n">
+        <v>45288</v>
+      </c>
+      <c r="S31" t="b">
+        <v>1</v>
+      </c>
+      <c r="T31" t="n">
+        <v>2</v>
+      </c>
+      <c r="U31" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="32">
@@ -2244,19 +2627,19 @@
         <v>5.89</v>
       </c>
       <c r="G32" s="1" t="n">
-        <v>45329.55208333334</v>
+        <v>45330.38541666666</v>
       </c>
       <c r="H32" t="n">
-        <v>2299.75</v>
+        <v>2247.15</v>
       </c>
       <c r="I32" t="n">
         <v>2268.886954133802</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>35.16666666666666</v>
+        <v>36</v>
       </c>
       <c r="K32" t="n">
-        <v>12.02</v>
+        <v>9.460000000000001</v>
       </c>
       <c r="L32" t="n">
         <v>2.23</v>
@@ -2265,7 +2648,7 @@
         <v>0.65</v>
       </c>
       <c r="N32" t="n">
-        <v>3.27</v>
+        <v>3.47</v>
       </c>
       <c r="O32" t="n">
         <v>1.85</v>
@@ -2274,7 +2657,19 @@
         <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>50</v>
+        <v>51</v>
+      </c>
+      <c r="R32" s="3" t="n">
+        <v>45316</v>
+      </c>
+      <c r="S32" t="b">
+        <v>1</v>
+      </c>
+      <c r="T32" t="n">
+        <v>2</v>
+      </c>
+      <c r="U32" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="33">
@@ -2301,28 +2696,28 @@
         <v>7.79</v>
       </c>
       <c r="G33" s="1" t="n">
-        <v>45343.55208333334</v>
+        <v>45344.38541666666</v>
       </c>
       <c r="H33" t="n">
-        <v>2337</v>
+        <v>2372.75</v>
       </c>
       <c r="I33" t="n">
         <v>2363.16621690786</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>13.16666666666667</v>
+        <v>14</v>
       </c>
       <c r="K33" t="n">
-        <v>-4</v>
+        <v>-5.59</v>
       </c>
       <c r="L33" t="n">
-        <v>5.42</v>
+        <v>6.35</v>
       </c>
       <c r="M33" t="n">
         <v>0.67</v>
       </c>
       <c r="N33" t="n">
-        <v>2.01</v>
+        <v>2.34</v>
       </c>
       <c r="O33" t="n">
         <v>-3.47</v>
@@ -2331,7 +2726,19 @@
         <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R33" s="3" t="n">
+        <v>45351</v>
+      </c>
+      <c r="S33" t="b">
+        <v>0</v>
+      </c>
+      <c r="T33" t="n">
+        <v>1</v>
+      </c>
+      <c r="U33" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="34">
@@ -2358,22 +2765,22 @@
         <v>6.46</v>
       </c>
       <c r="G34" s="1" t="n">
-        <v>45362.55208333334</v>
+        <v>45363.38541666666</v>
       </c>
       <c r="H34" t="n">
-        <v>2424</v>
+        <v>2333.75</v>
       </c>
       <c r="I34" t="n">
         <v>2336.707676150211</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>18.16666666666667</v>
+        <v>19</v>
       </c>
       <c r="K34" t="n">
-        <v>2.16</v>
+        <v>-1.64</v>
       </c>
       <c r="L34" t="n">
-        <v>1.8</v>
+        <v>2.32</v>
       </c>
       <c r="M34" t="n">
         <v>0.2</v>
@@ -2388,7 +2795,19 @@
         <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="R34" s="3" t="n">
+        <v>45351</v>
+      </c>
+      <c r="S34" t="b">
+        <v>1</v>
+      </c>
+      <c r="T34" t="n">
+        <v>2</v>
+      </c>
+      <c r="U34" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="35">
@@ -2415,19 +2834,19 @@
         <v>9.52</v>
       </c>
       <c r="G35" s="1" t="n">
-        <v>45378.55208333334</v>
+        <v>45379.38541666666</v>
       </c>
       <c r="H35" t="n">
-        <v>2274</v>
+        <v>2309</v>
       </c>
       <c r="I35" t="n">
         <v>2299.799607884049</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>15.16666666666667</v>
+        <v>16</v>
       </c>
       <c r="K35" t="n">
-        <v>2.56</v>
+        <v>1.06</v>
       </c>
       <c r="L35" t="n">
         <v>4.55</v>
@@ -2445,7 +2864,19 @@
         <v>1</v>
       </c>
       <c r="Q35" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R35" s="3" t="n">
+        <v>45379</v>
+      </c>
+      <c r="S35" t="b">
+        <v>0</v>
+      </c>
+      <c r="T35" t="n">
+        <v>1</v>
+      </c>
+      <c r="U35" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="36">
@@ -2472,19 +2903,19 @@
         <v>7.29</v>
       </c>
       <c r="G36" s="1" t="n">
-        <v>45446.55208333334</v>
+        <v>45447.38541666666</v>
       </c>
       <c r="H36" t="n">
-        <v>2973</v>
+        <v>2646.95</v>
       </c>
       <c r="I36" t="n">
         <v>2757.789614162496</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>67.16666666666667</v>
+        <v>68</v>
       </c>
       <c r="K36" t="n">
-        <v>28.76</v>
+        <v>14.64</v>
       </c>
       <c r="L36" t="n">
         <v>2.62</v>
@@ -2493,7 +2924,7 @@
         <v>2.25</v>
       </c>
       <c r="N36" t="n">
-        <v>4.04</v>
+        <v>12.55</v>
       </c>
       <c r="O36" t="n">
         <v>1.06</v>
@@ -2502,7 +2933,19 @@
         <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>87</v>
+        <v>88</v>
+      </c>
+      <c r="R36" s="3" t="n">
+        <v>45407</v>
+      </c>
+      <c r="S36" t="b">
+        <v>1</v>
+      </c>
+      <c r="T36" t="n">
+        <v>3</v>
+      </c>
+      <c r="U36" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="37">
@@ -2529,19 +2972,19 @@
         <v>15.93</v>
       </c>
       <c r="G37" s="1" t="n">
-        <v>45455.38541666666</v>
+        <v>45455.55208333334</v>
       </c>
       <c r="H37" t="n">
-        <v>2905</v>
+        <v>2924.8</v>
       </c>
       <c r="I37" t="n">
         <v>2919.27664627554</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>8</v>
+        <v>8.166666666666666</v>
       </c>
       <c r="K37" t="n">
-        <v>-9.75</v>
+        <v>-10.5</v>
       </c>
       <c r="L37" t="n">
         <v>11.45</v>
@@ -2559,7 +3002,19 @@
         <v>1</v>
       </c>
       <c r="Q37" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R37" s="3" t="n">
+        <v>45470</v>
+      </c>
+      <c r="S37" t="b">
+        <v>0</v>
+      </c>
+      <c r="T37" t="n">
+        <v>1</v>
+      </c>
+      <c r="U37" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="38">
@@ -2586,19 +3041,19 @@
         <v>8.4</v>
       </c>
       <c r="G38" s="1" t="n">
-        <v>45496.38541666666</v>
+        <v>45496.55208333334</v>
       </c>
       <c r="H38" t="n">
-        <v>3235</v>
+        <v>3134.5</v>
       </c>
       <c r="I38" t="n">
         <v>3208.944023758957</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>40.83333333333334</v>
+        <v>41</v>
       </c>
       <c r="K38" t="n">
-        <v>10.61</v>
+        <v>7.17</v>
       </c>
       <c r="L38" t="n">
         <v>0.75</v>
@@ -2616,7 +3071,19 @@
         <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>54</v>
+        <v>55</v>
+      </c>
+      <c r="R38" s="3" t="n">
+        <v>45470</v>
+      </c>
+      <c r="S38" t="b">
+        <v>1</v>
+      </c>
+      <c r="T38" t="n">
+        <v>2</v>
+      </c>
+      <c r="U38" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="39">
@@ -2643,19 +3110,19 @@
         <v>9.75</v>
       </c>
       <c r="G39" s="1" t="n">
-        <v>45555.38541666666</v>
+        <v>45555.55208333334</v>
       </c>
       <c r="H39" t="n">
-        <v>2928</v>
+        <v>2991</v>
       </c>
       <c r="I39" t="n">
         <v>2986.678437590323</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>58.83333333333334</v>
+        <v>59</v>
       </c>
       <c r="K39" t="n">
-        <v>6.59</v>
+        <v>4.58</v>
       </c>
       <c r="L39" t="n">
         <v>5.23</v>
@@ -2673,7 +3140,19 @@
         <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>84</v>
+        <v>85</v>
+      </c>
+      <c r="R39" s="3" t="n">
+        <v>45498</v>
+      </c>
+      <c r="S39" t="b">
+        <v>1</v>
+      </c>
+      <c r="T39" t="n">
+        <v>3</v>
+      </c>
+      <c r="U39" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="40">
@@ -2700,28 +3179,28 @@
         <v>7.51</v>
       </c>
       <c r="G40" s="1" t="n">
-        <v>45566.55208333334</v>
+        <v>45568.38541666666</v>
       </c>
       <c r="H40" t="n">
-        <v>3260</v>
+        <v>3101.25</v>
       </c>
       <c r="I40" t="n">
         <v>3102.167379676057</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>11</v>
+        <v>12.83333333333333</v>
       </c>
       <c r="K40" t="n">
-        <v>8.99</v>
+        <v>3.69</v>
       </c>
       <c r="L40" t="n">
         <v>3.14</v>
       </c>
       <c r="M40" t="n">
-        <v>1.41</v>
+        <v>2.45</v>
       </c>
       <c r="N40" t="n">
-        <v>3.28</v>
+        <v>6.19</v>
       </c>
       <c r="O40" t="n">
         <v>2.61</v>
@@ -2730,7 +3209,19 @@
         <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R40" s="3" t="n">
+        <v>45561</v>
+      </c>
+      <c r="S40" t="b">
+        <v>1</v>
+      </c>
+      <c r="T40" t="n">
+        <v>2</v>
+      </c>
+      <c r="U40" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="41">
@@ -2757,19 +3248,19 @@
         <v>10.56</v>
       </c>
       <c r="G41" s="1" t="n">
-        <v>45579.38541666666</v>
+        <v>45579.55208333334</v>
       </c>
       <c r="H41" t="n">
-        <v>3038.1</v>
+        <v>3094.85</v>
       </c>
       <c r="I41" t="n">
         <v>3093.890586427553</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>11</v>
+        <v>11.16666666666667</v>
       </c>
       <c r="K41" t="n">
-        <v>2.04</v>
+        <v>0.21</v>
       </c>
       <c r="L41" t="n">
         <v>5.18</v>
@@ -2787,7 +3278,19 @@
         <v>1</v>
       </c>
       <c r="Q41" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R41" s="3" t="n">
+        <v>45596</v>
+      </c>
+      <c r="S41" t="b">
+        <v>0</v>
+      </c>
+      <c r="T41" t="n">
+        <v>1</v>
+      </c>
+      <c r="U41" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="42">
@@ -2814,22 +3317,22 @@
         <v>7.06</v>
       </c>
       <c r="G42" s="1" t="n">
-        <v>45586.55208333334</v>
+        <v>45587.38541666666</v>
       </c>
       <c r="H42" t="n">
-        <v>3039.9</v>
+        <v>2937.95</v>
       </c>
       <c r="I42" t="n">
         <v>3014.727062772587</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>7</v>
+        <v>7.833333333333333</v>
       </c>
       <c r="K42" t="n">
-        <v>-1.78</v>
+        <v>-5.07</v>
       </c>
       <c r="L42" t="n">
-        <v>3.03</v>
+        <v>5.31</v>
       </c>
       <c r="M42" t="n">
         <v>-0</v>
@@ -2844,7 +3347,19 @@
         <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R42" s="3" t="n">
+        <v>45596</v>
+      </c>
+      <c r="S42" t="b">
+        <v>0</v>
+      </c>
+      <c r="T42" t="n">
+        <v>1</v>
+      </c>
+      <c r="U42" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="43">
@@ -2871,19 +3386,19 @@
         <v>10.8</v>
       </c>
       <c r="G43" s="1" t="n">
-        <v>45617.55208333334</v>
+        <v>45618.38541666666</v>
       </c>
       <c r="H43" t="n">
-        <v>2711</v>
+        <v>2839.2</v>
       </c>
       <c r="I43" t="n">
         <v>2771.357111405672</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>30.16666666666667</v>
+        <v>31</v>
       </c>
       <c r="K43" t="n">
-        <v>7.72</v>
+        <v>3.36</v>
       </c>
       <c r="L43" t="n">
         <v>5.22</v>
@@ -2892,7 +3407,7 @@
         <v>0.99</v>
       </c>
       <c r="N43" t="n">
-        <v>1.69</v>
+        <v>5.39</v>
       </c>
       <c r="O43" t="n">
         <v>-4.24</v>
@@ -2901,7 +3416,19 @@
         <v>1</v>
       </c>
       <c r="Q43" t="n">
-        <v>41</v>
+        <v>42</v>
+      </c>
+      <c r="R43" s="3" t="n">
+        <v>45596</v>
+      </c>
+      <c r="S43" t="b">
+        <v>1</v>
+      </c>
+      <c r="T43" t="n">
+        <v>2</v>
+      </c>
+      <c r="U43" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="44">
@@ -2928,19 +3455,19 @@
         <v>10.1</v>
       </c>
       <c r="G44" s="1" t="n">
-        <v>45650.55208333334</v>
+        <v>45652.38541666666</v>
       </c>
       <c r="H44" t="n">
-        <v>2859.6</v>
+        <v>2828.95</v>
       </c>
       <c r="I44" t="n">
         <v>2835.485311238713</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>32.16666666666666</v>
+        <v>34</v>
       </c>
       <c r="K44" t="n">
-        <v>0.72</v>
+        <v>-0.36</v>
       </c>
       <c r="L44" t="n">
         <v>4.9</v>
@@ -2958,7 +3485,19 @@
         <v>1</v>
       </c>
       <c r="Q44" t="n">
-        <v>46</v>
+        <v>47</v>
+      </c>
+      <c r="R44" s="3" t="n">
+        <v>45624</v>
+      </c>
+      <c r="S44" t="b">
+        <v>1</v>
+      </c>
+      <c r="T44" t="n">
+        <v>2</v>
+      </c>
+      <c r="U44" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="45">
@@ -2985,19 +3524,19 @@
         <v>6.97</v>
       </c>
       <c r="G45" s="1" t="n">
-        <v>45686.55208333334</v>
+        <v>45687.38541666666</v>
       </c>
       <c r="H45" t="n">
-        <v>2237.65</v>
+        <v>2290.45</v>
       </c>
       <c r="I45" t="n">
         <v>2265.896382744465</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>34.16666666666666</v>
+        <v>35</v>
       </c>
       <c r="K45" t="n">
-        <v>20.9</v>
+        <v>19.04</v>
       </c>
       <c r="L45" t="n">
         <v>2.37</v>
@@ -3015,7 +3554,19 @@
         <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>50</v>
+        <v>51</v>
+      </c>
+      <c r="R45" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S45" t="b">
+        <v>0</v>
+      </c>
+      <c r="T45" t="n">
+        <v>1</v>
+      </c>
+      <c r="U45" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="46">
@@ -3042,22 +3593,22 @@
         <v>9.24</v>
       </c>
       <c r="G46" s="1" t="n">
-        <v>45695.55208333334</v>
+        <v>45698.38541666666</v>
       </c>
       <c r="H46" t="n">
-        <v>2197</v>
+        <v>2130.9</v>
       </c>
       <c r="I46" t="n">
         <v>2177.111207533421</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>8.166666666666666</v>
+        <v>11</v>
       </c>
       <c r="K46" t="n">
-        <v>-4.08</v>
+        <v>-6.97</v>
       </c>
       <c r="L46" t="n">
-        <v>4.53</v>
+        <v>7.27</v>
       </c>
       <c r="M46" t="n">
         <v>0.43</v>
@@ -3072,7 +3623,19 @@
         <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R46" s="3" t="n">
+        <v>45715</v>
+      </c>
+      <c r="S46" t="b">
+        <v>0</v>
+      </c>
+      <c r="T46" t="n">
+        <v>1</v>
+      </c>
+      <c r="U46" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="47">
@@ -3099,19 +3662,19 @@
         <v>11.98</v>
       </c>
       <c r="G47" s="1" t="n">
-        <v>45734.55208333334</v>
+        <v>45735.38541666666</v>
       </c>
       <c r="H47" t="n">
-        <v>2033.9</v>
+        <v>2094</v>
       </c>
       <c r="I47" t="n">
         <v>2093.570559071818</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>36.16666666666666</v>
+        <v>37</v>
       </c>
       <c r="K47" t="n">
-        <v>4.55</v>
+        <v>1.73</v>
       </c>
       <c r="L47" t="n">
         <v>3.74</v>
@@ -3129,7 +3692,19 @@
         <v>0</v>
       </c>
       <c r="Q47" t="n">
-        <v>50</v>
+        <v>51</v>
+      </c>
+      <c r="R47" s="3" t="n">
+        <v>45715</v>
+      </c>
+      <c r="S47" t="b">
+        <v>1</v>
+      </c>
+      <c r="T47" t="n">
+        <v>2</v>
+      </c>
+      <c r="U47" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="48">
@@ -3156,19 +3731,19 @@
         <v>8.42</v>
       </c>
       <c r="G48" s="1" t="n">
-        <v>45744.55208333334</v>
+        <v>45748.38541666666</v>
       </c>
       <c r="H48" t="n">
-        <v>2126.8</v>
+        <v>2052.8</v>
       </c>
       <c r="I48" t="n">
         <v>2053.193698074004</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>9.166666666666666</v>
+        <v>13</v>
       </c>
       <c r="K48" t="n">
-        <v>1.57</v>
+        <v>-1.97</v>
       </c>
       <c r="L48" t="n">
         <v>3.32</v>
@@ -3177,7 +3752,7 @@
         <v>1.36</v>
       </c>
       <c r="N48" t="n">
-        <v>2.74</v>
+        <v>3.76</v>
       </c>
       <c r="O48" t="n">
         <v>3.4</v>
@@ -3186,7 +3761,19 @@
         <v>0</v>
       </c>
       <c r="Q48" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R48" s="3" t="n">
+        <v>45743</v>
+      </c>
+      <c r="S48" t="b">
+        <v>1</v>
+      </c>
+      <c r="T48" t="n">
+        <v>2</v>
+      </c>
+      <c r="U48" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="49">
@@ -3213,22 +3800,22 @@
         <v>8.710000000000001</v>
       </c>
       <c r="G49" s="1" t="n">
-        <v>45769.55208333334</v>
+        <v>45770.38541666666</v>
       </c>
       <c r="H49" t="n">
-        <v>2095</v>
+        <v>2144</v>
       </c>
       <c r="I49" t="n">
         <v>2107.861129456757</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>21.16666666666667</v>
+        <v>22</v>
       </c>
       <c r="K49" t="n">
-        <v>-2.06</v>
+        <v>-4.44</v>
       </c>
       <c r="L49" t="n">
-        <v>5.97</v>
+        <v>6.24</v>
       </c>
       <c r="M49" t="n">
         <v>3.19</v>
@@ -3243,7 +3830,19 @@
         <v>0</v>
       </c>
       <c r="Q49" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R49" s="3" t="n">
+        <v>45771</v>
+      </c>
+      <c r="S49" t="b">
+        <v>0</v>
+      </c>
+      <c r="T49" t="n">
+        <v>1</v>
+      </c>
+      <c r="U49" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="50">
@@ -3270,22 +3869,22 @@
         <v>7.3</v>
       </c>
       <c r="G50" s="1" t="n">
-        <v>45785.38541666666</v>
+        <v>45785.55208333334</v>
       </c>
       <c r="H50" t="n">
-        <v>2090.9</v>
+        <v>2019</v>
       </c>
       <c r="I50" t="n">
         <v>2063.250031379226</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>15</v>
+        <v>15.16666666666667</v>
       </c>
       <c r="K50" t="n">
-        <v>-2.48</v>
+        <v>-5.83</v>
       </c>
       <c r="L50" t="n">
-        <v>4.26</v>
+        <v>6.44</v>
       </c>
       <c r="M50" t="n">
         <v>0.47</v>
@@ -3300,7 +3899,19 @@
         <v>0</v>
       </c>
       <c r="Q50" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="R50" s="3" t="n">
+        <v>45771</v>
+      </c>
+      <c r="S50" t="b">
+        <v>1</v>
+      </c>
+      <c r="T50" t="n">
+        <v>2</v>
+      </c>
+      <c r="U50" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="51">
@@ -3327,22 +3938,22 @@
         <v>10.81</v>
       </c>
       <c r="G51" s="1" t="n">
-        <v>45792.55208333334</v>
+        <v>45793.38541666666</v>
       </c>
       <c r="H51" t="n">
-        <v>2147.5</v>
+        <v>2177.9</v>
       </c>
       <c r="I51" t="n">
         <v>2174.009787329245</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>7</v>
+        <v>7.833333333333333</v>
       </c>
       <c r="K51" t="n">
-        <v>-6.36</v>
+        <v>-7.87</v>
       </c>
       <c r="L51" t="n">
-        <v>6.98</v>
+        <v>8.720000000000001</v>
       </c>
       <c r="M51" t="n">
         <v>3.79</v>
@@ -3357,7 +3968,19 @@
         <v>1</v>
       </c>
       <c r="Q51" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R51" s="3" t="n">
+        <v>45806</v>
+      </c>
+      <c r="S51" t="b">
+        <v>0</v>
+      </c>
+      <c r="T51" t="n">
+        <v>1</v>
+      </c>
+      <c r="U51" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="52">
@@ -3384,19 +4007,19 @@
         <v>7.62</v>
       </c>
       <c r="G52" s="1" t="n">
-        <v>45838.38541666666</v>
+        <v>45838.55208333334</v>
       </c>
       <c r="H52" t="n">
-        <v>2352.5</v>
+        <v>2339</v>
       </c>
       <c r="I52" t="n">
         <v>2341.265632054893</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>45</v>
+        <v>45.16666666666666</v>
       </c>
       <c r="K52" t="n">
-        <v>8.02</v>
+        <v>7.4</v>
       </c>
       <c r="L52" t="n">
         <v>1.69</v>
@@ -3414,7 +4037,19 @@
         <v>0</v>
       </c>
       <c r="Q52" t="n">
-        <v>63</v>
+        <v>64</v>
+      </c>
+      <c r="R52" s="3" t="n">
+        <v>45806</v>
+      </c>
+      <c r="S52" t="b">
+        <v>1</v>
+      </c>
+      <c r="T52" t="n">
+        <v>3</v>
+      </c>
+      <c r="U52" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="53">
@@ -3441,25 +4076,25 @@
         <v>5.38</v>
       </c>
       <c r="G53" s="1" t="n">
-        <v>45854.55208333334</v>
+        <v>45855.38541666666</v>
       </c>
       <c r="H53" t="n">
-        <v>2288</v>
+        <v>2325.3</v>
       </c>
       <c r="I53" t="n">
         <v>2320.497452665907</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>16</v>
+        <v>16.83333333333333</v>
       </c>
       <c r="K53" t="n">
-        <v>2.18</v>
+        <v>0.59</v>
       </c>
       <c r="L53" t="n">
         <v>1.11</v>
       </c>
       <c r="M53" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.92</v>
       </c>
       <c r="N53" t="n">
         <v>2.5</v>
@@ -3471,7 +4106,19 @@
         <v>0</v>
       </c>
       <c r="Q53" t="n">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="R53" s="3" t="n">
+        <v>45869</v>
+      </c>
+      <c r="S53" t="b">
+        <v>0</v>
+      </c>
+      <c r="T53" t="n">
+        <v>1</v>
+      </c>
+      <c r="U53" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="54">
@@ -3498,28 +4145,28 @@
         <v>5.03</v>
       </c>
       <c r="G54" s="1" t="n">
-        <v>45862.55208333334</v>
+        <v>45863.38541666666</v>
       </c>
       <c r="H54" t="n">
-        <v>2310</v>
+        <v>2233.8</v>
       </c>
       <c r="I54" t="n">
         <v>2289.605581469536</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>7.166666666666667</v>
+        <v>8</v>
       </c>
       <c r="K54" t="n">
-        <v>-0.66</v>
+        <v>-3.93</v>
       </c>
       <c r="L54" t="n">
-        <v>1.43</v>
+        <v>3.98</v>
       </c>
       <c r="M54" t="n">
         <v>0.5</v>
       </c>
       <c r="N54" t="n">
-        <v>1.67</v>
+        <v>3.46</v>
       </c>
       <c r="O54" t="n">
         <v>2.32</v>
@@ -3528,7 +4175,19 @@
         <v>0</v>
       </c>
       <c r="Q54" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R54" s="3" t="n">
+        <v>45869</v>
+      </c>
+      <c r="S54" t="b">
+        <v>0</v>
+      </c>
+      <c r="T54" t="n">
+        <v>1</v>
+      </c>
+      <c r="U54" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="55">
@@ -3555,19 +4214,19 @@
         <v>6.72</v>
       </c>
       <c r="G55" s="1" t="n">
-        <v>45889.55208333334</v>
+        <v>45890.38541666666</v>
       </c>
       <c r="H55" t="n">
-        <v>2039.5</v>
+        <v>2071.7</v>
       </c>
       <c r="I55" t="n">
         <v>2048.348333242287</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>26.16666666666667</v>
+        <v>27</v>
       </c>
       <c r="K55" t="n">
-        <v>8.699999999999999</v>
+        <v>7.26</v>
       </c>
       <c r="L55" t="n">
         <v>3.36</v>
@@ -3585,7 +4244,19 @@
         <v>0</v>
       </c>
       <c r="Q55" t="n">
-        <v>36</v>
+        <v>37</v>
+      </c>
+      <c r="R55" s="3" t="n">
+        <v>45869</v>
+      </c>
+      <c r="S55" t="b">
+        <v>1</v>
+      </c>
+      <c r="T55" t="n">
+        <v>2</v>
+      </c>
+      <c r="U55" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="56">
@@ -3612,22 +4283,22 @@
         <v>5.48</v>
       </c>
       <c r="G56" s="1" t="n">
-        <v>45895.55208333334</v>
+        <v>45897.38541666666</v>
       </c>
       <c r="H56" t="n">
-        <v>2002.3</v>
+        <v>1974</v>
       </c>
       <c r="I56" t="n">
         <v>1977.109702798484</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>5.166666666666667</v>
+        <v>7</v>
       </c>
       <c r="K56" t="n">
-        <v>-3.35</v>
+        <v>-4.72</v>
       </c>
       <c r="L56" t="n">
-        <v>3.46</v>
+        <v>4.89</v>
       </c>
       <c r="M56" t="n">
         <v>-0</v>
@@ -3642,7 +4313,19 @@
         <v>0</v>
       </c>
       <c r="Q56" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R56" s="3" t="n">
+        <v>45897</v>
+      </c>
+      <c r="S56" t="b">
+        <v>0</v>
+      </c>
+      <c r="T56" t="n">
+        <v>1</v>
+      </c>
+      <c r="U56" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="57">
@@ -3669,19 +4352,19 @@
         <v>6.29</v>
       </c>
       <c r="G57" s="1" t="n">
-        <v>45912.55208333334</v>
+        <v>45915.38541666666</v>
       </c>
       <c r="H57" t="n">
-        <v>1999.8</v>
+        <v>2047</v>
       </c>
       <c r="I57" t="n">
         <v>2037.867937592502</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>15.16666666666667</v>
+        <v>18</v>
       </c>
       <c r="K57" t="n">
-        <v>-1.31</v>
+        <v>-3.7</v>
       </c>
       <c r="L57" t="n">
         <v>4.3</v>
@@ -3699,7 +4382,19 @@
         <v>0</v>
       </c>
       <c r="Q57" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R57" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S57" t="b">
+        <v>0</v>
+      </c>
+      <c r="T57" t="n">
+        <v>1</v>
+      </c>
+      <c r="U57" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="58">
@@ -3726,19 +4421,19 @@
         <v>5.29</v>
       </c>
       <c r="G58" s="1" t="n">
-        <v>45923.55208333334</v>
+        <v>45924.38541666666</v>
       </c>
       <c r="H58" t="n">
-        <v>2106.3</v>
+        <v>2033.7</v>
       </c>
       <c r="I58" t="n">
         <v>2054.67343315447</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>8.166666666666666</v>
+        <v>9</v>
       </c>
       <c r="K58" t="n">
-        <v>2.9</v>
+        <v>-0.65</v>
       </c>
       <c r="L58" t="n">
         <v>2.14</v>
@@ -3747,7 +4442,7 @@
         <v>0.38</v>
       </c>
       <c r="N58" t="n">
-        <v>1.87</v>
+        <v>4.1</v>
       </c>
       <c r="O58" t="n">
         <v>2.01</v>
@@ -3756,7 +4451,19 @@
         <v>0</v>
       </c>
       <c r="Q58" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R58" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S58" t="b">
+        <v>0</v>
+      </c>
+      <c r="T58" t="n">
+        <v>1</v>
+      </c>
+      <c r="U58" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="59">
@@ -3783,19 +4490,19 @@
         <v>6.94</v>
       </c>
       <c r="G59" s="1" t="n">
-        <v>45937.38541666666</v>
+        <v>45937.55208333334</v>
       </c>
       <c r="H59" t="n">
-        <v>2057.8</v>
+        <v>2075</v>
       </c>
       <c r="I59" t="n">
         <v>2065.511182919828</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>13</v>
+        <v>13.16666666666667</v>
       </c>
       <c r="K59" t="n">
-        <v>-1.19</v>
+        <v>-2.03</v>
       </c>
       <c r="L59" t="n">
         <v>4.01</v>
@@ -3813,7 +4520,19 @@
         <v>1</v>
       </c>
       <c r="Q59" t="n">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="R59" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S59" t="b">
+        <v>1</v>
+      </c>
+      <c r="T59" t="n">
+        <v>2</v>
+      </c>
+      <c r="U59" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="60">
@@ -3840,19 +4559,19 @@
         <v>4.88</v>
       </c>
       <c r="G60" s="1" t="n">
-        <v>45967.38541666666</v>
+        <v>45967.55208333334</v>
       </c>
       <c r="H60" t="n">
-        <v>2235</v>
+        <v>2193.5</v>
       </c>
       <c r="I60" t="n">
         <v>2204.457806546622</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>29.83333333333333</v>
+        <v>30</v>
       </c>
       <c r="K60" t="n">
-        <v>7.71</v>
+        <v>5.71</v>
       </c>
       <c r="L60" t="n">
         <v>3.23</v>
@@ -3870,7 +4589,19 @@
         <v>0</v>
       </c>
       <c r="Q60" t="n">
-        <v>39</v>
+        <v>40</v>
+      </c>
+      <c r="R60" s="3" t="n">
+        <v>45958</v>
+      </c>
+      <c r="S60" t="b">
+        <v>1</v>
+      </c>
+      <c r="T60" t="n">
+        <v>2</v>
+      </c>
+      <c r="U60" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="61">
@@ -3897,19 +4628,19 @@
         <v>7.12</v>
       </c>
       <c r="G61" s="1" t="n">
-        <v>46023.55208333334</v>
+        <v>46024.38541666666</v>
       </c>
       <c r="H61" t="n">
-        <v>2022</v>
+        <v>2063.5</v>
       </c>
       <c r="I61" t="n">
         <v>2041.633649249946</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>56</v>
+        <v>56.83333333333334</v>
       </c>
       <c r="K61" t="n">
-        <v>7.82</v>
+        <v>5.93</v>
       </c>
       <c r="L61" t="n">
         <v>2.03</v>
@@ -3927,7 +4658,19 @@
         <v>1</v>
       </c>
       <c r="Q61" t="n">
-        <v>79</v>
+        <v>80</v>
+      </c>
+      <c r="R61" s="3" t="n">
+        <v>45986</v>
+      </c>
+      <c r="S61" t="b">
+        <v>1</v>
+      </c>
+      <c r="T61" t="n">
+        <v>3</v>
+      </c>
+      <c r="U61" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="62">
@@ -3954,28 +4697,28 @@
         <v>4.69</v>
       </c>
       <c r="G62" s="1" t="n">
-        <v>46030.55208333334</v>
+        <v>46031.38541666666</v>
       </c>
       <c r="H62" t="n">
-        <v>2090.1</v>
+        <v>1998.3</v>
       </c>
       <c r="I62" t="n">
         <v>2040.918840415794</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>6.166666666666667</v>
+        <v>7</v>
       </c>
       <c r="K62" t="n">
-        <v>1.29</v>
+        <v>-3.16</v>
       </c>
       <c r="L62" t="n">
-        <v>2.2</v>
+        <v>3.62</v>
       </c>
       <c r="M62" t="n">
         <v>0.62</v>
       </c>
       <c r="N62" t="n">
-        <v>2.33</v>
+        <v>4.7</v>
       </c>
       <c r="O62" t="n">
         <v>2.37</v>
@@ -3984,7 +4727,19 @@
         <v>0</v>
       </c>
       <c r="Q62" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R62" s="3" t="n">
+        <v>46049</v>
+      </c>
+      <c r="S62" t="b">
+        <v>0</v>
+      </c>
+      <c r="T62" t="n">
+        <v>1</v>
+      </c>
+      <c r="U62" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="63">
@@ -4011,28 +4766,28 @@
         <v>8.140000000000001</v>
       </c>
       <c r="G63" s="1" t="n">
-        <v>46055.55208333334</v>
+        <v>46056.38541666666</v>
       </c>
       <c r="H63" t="n">
-        <v>1566.2</v>
+        <v>1677.4</v>
       </c>
       <c r="I63" t="n">
         <v>1660.200366456355</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>24.16666666666667</v>
+        <v>25</v>
       </c>
       <c r="K63" t="n">
-        <v>21.62</v>
+        <v>16.06</v>
       </c>
       <c r="L63" t="n">
         <v>4.59</v>
       </c>
       <c r="M63" t="n">
-        <v>1.03</v>
+        <v>2.92</v>
       </c>
       <c r="N63" t="n">
-        <v>4</v>
+        <v>8.41</v>
       </c>
       <c r="O63" t="n">
         <v>-4.7</v>
@@ -4041,7 +4796,19 @@
         <v>1</v>
       </c>
       <c r="Q63" t="n">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="R63" s="3" t="n">
+        <v>46049</v>
+      </c>
+      <c r="S63" t="b">
+        <v>1</v>
+      </c>
+      <c r="T63" t="n">
+        <v>2</v>
+      </c>
+      <c r="U63" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="64">
@@ -4068,19 +4835,19 @@
         <v>10.89</v>
       </c>
       <c r="G64" s="1" t="n">
-        <v>46079.55208333334</v>
+        <v>46080.38541666666</v>
       </c>
       <c r="H64" t="n">
-        <v>1800</v>
+        <v>1761</v>
       </c>
       <c r="I64" t="n">
         <v>1767.101398398071</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>23.16666666666667</v>
+        <v>24</v>
       </c>
       <c r="K64" t="n">
-        <v>7.31</v>
+        <v>4.98</v>
       </c>
       <c r="L64" t="n">
         <v>4.01</v>
@@ -4089,7 +4856,7 @@
         <v>1.12</v>
       </c>
       <c r="N64" t="n">
-        <v>3.97</v>
+        <v>4.06</v>
       </c>
       <c r="O64" t="n">
         <v>8.41</v>
@@ -4098,7 +4865,19 @@
         <v>1</v>
       </c>
       <c r="Q64" t="n">
-        <v>36</v>
+        <v>37</v>
+      </c>
+      <c r="R64" s="3" t="n">
+        <v>46077</v>
+      </c>
+      <c r="S64" t="b">
+        <v>1</v>
+      </c>
+      <c r="T64" t="n">
+        <v>2</v>
+      </c>
+      <c r="U64" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="65">
@@ -4125,19 +4904,19 @@
         <v>7.52</v>
       </c>
       <c r="G65" s="1" t="n">
-        <v>46118.55208333334</v>
+        <v>46119.38541666666</v>
       </c>
       <c r="H65" t="n">
-        <v>1587</v>
+        <v>1599.4</v>
       </c>
       <c r="I65" t="n">
         <v>1587.937255465037</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>38.16666666666666</v>
+        <v>39</v>
       </c>
       <c r="K65" t="n">
-        <v>9.880000000000001</v>
+        <v>9.18</v>
       </c>
       <c r="L65" t="n">
         <v>2.26</v>
@@ -4155,7 +4934,19 @@
         <v>1</v>
       </c>
       <c r="Q65" t="n">
-        <v>46</v>
+        <v>47</v>
+      </c>
+      <c r="R65" s="3" t="n">
+        <v>46111</v>
+      </c>
+      <c r="S65" t="b">
+        <v>1</v>
+      </c>
+      <c r="T65" t="n">
+        <v>2</v>
+      </c>
+      <c r="U65" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="66">
@@ -4182,19 +4973,19 @@
         <v>10.35</v>
       </c>
       <c r="G66" s="1" t="n">
-        <v>46153.55208333334</v>
+        <v>46154.38541666666</v>
       </c>
       <c r="H66" t="n">
-        <v>1790.1</v>
+        <v>1736.7</v>
       </c>
       <c r="I66" t="n">
         <v>1770.189717372482</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>34.16666666666666</v>
+        <v>35</v>
       </c>
       <c r="K66" t="n">
-        <v>11.92</v>
+        <v>8.58</v>
       </c>
       <c r="L66" t="n">
         <v>3.35</v>
@@ -4212,7 +5003,19 @@
         <v>0</v>
       </c>
       <c r="Q66" t="n">
-        <v>46</v>
+        <v>47</v>
+      </c>
+      <c r="R66" s="3" t="n">
+        <v>46140</v>
+      </c>
+      <c r="S66" t="b">
+        <v>1</v>
+      </c>
+      <c r="T66" t="n">
+        <v>2</v>
+      </c>
+      <c r="U66" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="67">
@@ -4239,28 +5042,28 @@
         <v>9.67</v>
       </c>
       <c r="G67" s="1" t="n">
-        <v>46185.55208333334</v>
+        <v>46188.38541666666</v>
       </c>
       <c r="H67" t="n">
-        <v>1694.2</v>
+        <v>1779.4</v>
       </c>
       <c r="I67" t="n">
         <v>1718.594190451175</v>
       </c>
       <c r="J67" s="2" t="n">
-        <v>31.16666666666667</v>
+        <v>34</v>
       </c>
       <c r="K67" t="n">
-        <v>2.45</v>
+        <v>-2.46</v>
       </c>
       <c r="L67" t="n">
         <v>5.65</v>
       </c>
       <c r="M67" t="n">
-        <v>1.64</v>
+        <v>1.94</v>
       </c>
       <c r="N67" t="n">
-        <v>4.32</v>
+        <v>4.42</v>
       </c>
       <c r="O67" t="n">
         <v>-4.23</v>
@@ -4269,7 +5072,19 @@
         <v>1</v>
       </c>
       <c r="Q67" t="n">
-        <v>46</v>
+        <v>47</v>
+      </c>
+      <c r="R67" s="3" t="n">
+        <v>46168</v>
+      </c>
+      <c r="S67" t="b">
+        <v>1</v>
+      </c>
+      <c r="T67" t="n">
+        <v>2</v>
+      </c>
+      <c r="U67" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="68">
@@ -4296,19 +5111,19 @@
         <v>8.539999999999999</v>
       </c>
       <c r="G68" s="1" t="n">
-        <v>46226.55208333334</v>
+        <v>46227.38541666666</v>
       </c>
       <c r="H68" t="n">
-        <v>2045</v>
+        <v>2028.7</v>
       </c>
       <c r="I68" t="n">
         <v>2041.447933588864</v>
       </c>
       <c r="J68" s="2" t="n">
-        <v>38.16666666666666</v>
+        <v>39</v>
       </c>
       <c r="K68" t="n">
-        <v>14.93</v>
+        <v>14.01</v>
       </c>
       <c r="L68" t="n">
         <v>3.16</v>
@@ -4326,7 +5141,19 @@
         <v>1</v>
       </c>
       <c r="Q68" t="n">
-        <v>56</v>
+        <v>57</v>
+      </c>
+      <c r="R68" s="3" t="n">
+        <v>46203</v>
+      </c>
+      <c r="S68" t="b">
+        <v>1</v>
+      </c>
+      <c r="T68" t="n">
+        <v>2</v>
+      </c>
+      <c r="U68" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="69">
@@ -4353,22 +5180,22 @@
         <v>4.89</v>
       </c>
       <c r="G69" s="1" t="n">
-        <v>46231.38541666666</v>
+        <v>46231.55208333334</v>
       </c>
       <c r="H69" t="n">
-        <v>2114.9</v>
+        <v>2137.7</v>
       </c>
       <c r="I69" t="n">
         <v>2127.959435195111</v>
       </c>
       <c r="J69" s="2" t="n">
-        <v>4</v>
+        <v>4.166666666666667</v>
       </c>
       <c r="K69" t="n">
-        <v>-4.25</v>
+        <v>-5.37</v>
       </c>
       <c r="L69" t="n">
-        <v>5.43</v>
+        <v>5.68</v>
       </c>
       <c r="M69" t="n">
         <v>0</v>
@@ -4383,7 +5210,19 @@
         <v>0</v>
       </c>
       <c r="Q69" t="n">
-        <v>5</v>
+        <v>6</v>
+      </c>
+      <c r="R69" s="3" t="n">
+        <v>46231</v>
+      </c>
+      <c r="S69" t="b">
+        <v>0</v>
+      </c>
+      <c r="T69" t="n">
+        <v>1</v>
+      </c>
+      <c r="U69" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="70">
@@ -4410,22 +5249,22 @@
         <v>7.34</v>
       </c>
       <c r="G70" s="1" t="n">
-        <v>46245.55208333334</v>
+        <v>46246.38541666666</v>
       </c>
       <c r="H70" t="n">
-        <v>2033.5</v>
+        <v>1988.6</v>
       </c>
       <c r="I70" t="n">
         <v>2015.583165550475</v>
       </c>
       <c r="J70" s="2" t="n">
-        <v>14</v>
+        <v>14.83333333333333</v>
       </c>
       <c r="K70" t="n">
-        <v>-4.87</v>
+        <v>-6.97</v>
       </c>
       <c r="L70" t="n">
-        <v>6.91</v>
+        <v>7.19</v>
       </c>
       <c r="M70" t="n">
         <v>0.67</v>
@@ -4440,7 +5279,19 @@
         <v>0</v>
       </c>
       <c r="Q70" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="R70" s="3" t="n">
+        <v>46259</v>
+      </c>
+      <c r="S70" t="b">
+        <v>0</v>
+      </c>
+      <c r="T70" t="n">
+        <v>1</v>
+      </c>
+      <c r="U70" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="71">
@@ -4467,19 +5318,19 @@
         <v>7.81</v>
       </c>
       <c r="G71" s="1" t="n">
-        <v>46309.55208333334</v>
+        <v>46310.38541666666</v>
       </c>
       <c r="H71" t="n">
-        <v>1570.2</v>
+        <v>1627.8</v>
       </c>
       <c r="I71" t="n">
         <v>1621.442315033226</v>
       </c>
       <c r="J71" s="2" t="n">
-        <v>63.16666666666666</v>
+        <v>64</v>
       </c>
       <c r="K71" t="n">
-        <v>21.04</v>
+        <v>18.14</v>
       </c>
       <c r="L71" t="n">
         <v>5.35</v>
@@ -4497,7 +5348,19 @@
         <v>0</v>
       </c>
       <c r="Q71" t="n">
-        <v>88</v>
+        <v>89</v>
+      </c>
+      <c r="R71" s="3" t="n">
+        <v>46259</v>
+      </c>
+      <c r="S71" t="b">
+        <v>1</v>
+      </c>
+      <c r="T71" t="n">
+        <v>3</v>
+      </c>
+      <c r="U71" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="72">
@@ -4524,28 +5387,28 @@
         <v>7.04</v>
       </c>
       <c r="G72" s="1" t="n">
-        <v>46317.55208333334</v>
+        <v>46318.38541666666</v>
       </c>
       <c r="H72" t="n">
-        <v>1564</v>
+        <v>1489.9</v>
       </c>
       <c r="I72" t="n">
         <v>1529.992668506427</v>
       </c>
       <c r="J72" s="2" t="n">
-        <v>7.166666666666667</v>
+        <v>8</v>
       </c>
       <c r="K72" t="n">
-        <v>-3.92</v>
+        <v>-8.470000000000001</v>
       </c>
       <c r="L72" t="n">
-        <v>5.58</v>
+        <v>9.789999999999999</v>
       </c>
       <c r="M72" t="n">
         <v>-0</v>
       </c>
       <c r="N72" t="n">
-        <v>1.99</v>
+        <v>4.28</v>
       </c>
       <c r="O72" t="n">
         <v>2.53</v>
@@ -4554,7 +5417,19 @@
         <v>0</v>
       </c>
       <c r="Q72" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R72" s="3" t="n">
+        <v>46322</v>
+      </c>
+      <c r="S72" t="b">
+        <v>0</v>
+      </c>
+      <c r="T72" t="n">
+        <v>1</v>
+      </c>
+      <c r="U72" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="73">
@@ -4605,6 +5480,12 @@
       <c r="Q73" t="n">
         <v>6</v>
       </c>
+      <c r="R73" s="3" t="n">
+        <v>46322</v>
+      </c>
+      <c r="S73" t="inlineStr"/>
+      <c r="T73" t="inlineStr"/>
+      <c r="U73" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -6707,7 +7588,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>23.6</v>
+        <v>24.6</v>
       </c>
     </row>
     <row r="6">
@@ -6717,7 +7598,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>21.2</v>
+        <v>22</v>
       </c>
     </row>
     <row r="7">
@@ -6727,7 +7608,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>83.2</v>
+        <v>84</v>
       </c>
     </row>
     <row r="8">
@@ -6737,7 +7618,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="9">
@@ -6747,7 +7628,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>33.2</v>
+        <v>34.5</v>
       </c>
     </row>
     <row r="10">
@@ -6757,7 +7638,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>45</v>
+        <v>45.2</v>
       </c>
     </row>
     <row r="11">
@@ -6797,7 +7678,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>3.9</v>
+        <v>1.01</v>
       </c>
     </row>
     <row r="15">
@@ -6807,7 +7688,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>4.35</v>
+        <v>0.9399999999999999</v>
       </c>
     </row>
     <row r="16">
@@ -6817,7 +7698,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>3.43</v>
+        <v>1.07</v>
       </c>
     </row>
     <row r="17">
@@ -6827,7 +7708,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>28.76</v>
+        <v>19.04</v>
       </c>
     </row>
     <row r="18">
@@ -6837,7 +7718,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>63.4</v>
+        <v>45.1</v>
       </c>
     </row>
     <row r="19">
@@ -6847,7 +7728,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>3.96</v>
+        <v>4.73</v>
       </c>
     </row>
     <row r="20">
@@ -6857,7 +7738,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>3.76</v>
+        <v>4.2</v>
       </c>
     </row>
     <row r="21">
@@ -6867,7 +7748,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>11.45</v>
+        <v>15.18</v>
       </c>
     </row>
     <row r="22">
@@ -6877,7 +7758,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
     </row>
     <row r="23">
@@ -6887,7 +7768,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="24">
@@ -6897,7 +7778,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1.3</v>
+        <v>1.51</v>
       </c>
     </row>
     <row r="25">
@@ -6907,7 +7788,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>5.38</v>
+        <v>9.789999999999999</v>
       </c>
     </row>
     <row r="26">
@@ -6917,7 +7798,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>3.73</v>
+        <v>4.42</v>
       </c>
     </row>
     <row r="27">
@@ -6927,7 +7808,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>7.19</v>
+        <v>12.55</v>
       </c>
     </row>
     <row r="28">
@@ -6937,7 +7818,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>26</v>
+        <v>36</v>
       </c>
     </row>
     <row r="29">
